--- a/public/templates/RadiographyFixed_Template_NoTimer.xlsx
+++ b/public/templates/RadiographyFixed_Template_NoTimer.xlsx
@@ -1055,7 +1055,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>mA Station 1</v>
+        <v>mAs Station 1</v>
       </c>
       <c r="B24" t="str">
         <v>50</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>mA Station 2</v>
+        <v>mAs Station 2</v>
       </c>
       <c r="B25" t="str">
         <v>100</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>mA Station 3</v>
+        <v>mAs Station 3</v>
       </c>
       <c r="B26" t="str">
         <v>23</v>
